--- a/fix-private-repos/issues_list.xlsx
+++ b/fix-private-repos/issues_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,42 +464,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>bf7c05e8-510d-4449-9e81-4c358ff3f440</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Tentative dataset should not have a version</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>69268e35-08ac-4e6d-b489-4bb72ac117b1</t>
+          <t>11051c56-8d67-43fc-a13c-b706e851a5a4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
+          <t>Tentative dataset should not have a version</t>
         </is>
       </c>
     </row>
@@ -509,12 +509,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
+          <t>da040f55-984d-490d-b917-a67856de4bac</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -524,12 +524,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>da040f55-984d-490d-b917-a67856de4bac</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-zooplankton-microscopy-dataset returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -539,42 +539,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Metadata mismatch: version CKAN='2.0' | DataCite='1.0'</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
+          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1sqnqvcxxcuqjfqasluneu6r311tfiogw/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
+          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work 'https://drive.google.com/file/d/1blzfowqmictyuet4mnip2d2nnmd2pxjg/view?usp=sharing' in CKAN not found in DataCite</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -584,12 +584,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-zooplankton-microscopy-dataset returned status_code=404</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -599,522 +599,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>f1aee211-bfab-46fd-b650-c5cacb782f40</t>
+          <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>0</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>No version</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>2</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ee2eec87-7a78-4a7f-87b7-54347a6c3b2f</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>0</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>No version</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Metadata mismatch: title CKAN='Water Level Time Series, Choke Pass, Central Coast, BC, Canada (Provisional)' | DataCite='Water Level measured from a Pressure Tide Gauge Instrument Deployed in Choke Pass on Calvert Island Research'</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>7607322d-6dea-4758-a257-de8353c899c1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Metadata mismatch: author 'Hakai Institute' in CKAN record not found in DataCite</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>0</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>0</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ed22dc0f-f2cc-41e5-ac1c-893e1b65c6d0</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Metadata mismatch: license CKAN='CC-BY-NC-4.0' | DataCite='cc-by-4.0'</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ed22dc0f-f2cc-41e5-ac1c-893e1b65c6d0</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Metadata mismatch: related work 'https://hecate.hakai.org/auth/access-request.php?ref=10.21966/tqj2-wh77' in CKAN not found in DataCite</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>2</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ed22dc0f-f2cc-41e5-ac1c-893e1b65c6d0</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Metadata mismatch: related identifier 'https://drive.google.com/file/d/1tCkBSbg8viQE8RDHg-0B3K9qfWbKU_Em/view' (HasMetadata) in DataCite not found in CKAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>0</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>No version</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>0</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>0e92249d-74e1-4253-a8a5-876d08a8ff65</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/Biogeochemical-Sampling-of-28-Streams-on-Vancouver-Island returned status_code=404</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>0</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>No version</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>1</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Metadata mismatch: related identifier '10.21966/q31x-qg72' (References) in DataCite not found in CKAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>2</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>55e7c337-02e8-4200-8ea9-88241d978f96</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Metadata mismatch: related identifier '10.21966/v57r-g944' (References) in DataCite not found in CKAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>0</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>0</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>No DOI defined</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>1</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>No funder</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>0</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>No version</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>1</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>2</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>f9ff815c-c57a-4750-8f80-25f5e145c8c0</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Metadata mismatch: author 'Geospatial Technology Team' in CKAN record not found in DataCite</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>0</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>No version</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>1</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>c83b5cbf-cc8c-4676-823c-77e28c0ec9da</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Metadata mismatch: author 'Hakai Institute' in CKAN record not found in DataCite</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>0</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>No version</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>1</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>2</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>b36a7c12-cb56-46b7-8241-9b52ac30c766</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Metadata mismatch: author 'Geospatial Technology Team Hakai' in CKAN record not found in DataCite</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>0</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>No version</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>1</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>2</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>c2b05382-684f-4349-a64b-b20521223574</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial Technology Team' in CKAN record not found in DataCite</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>0</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>8882a149-fabd-4ecd-98d3-68a2a88aee38</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Invalid Resource URL: http://docs.turnerdesigns.com/t2/doc/manuals/998-7210.pdf returned status_code=timeout</t>
+          <t>Tentative dataset should not have a version</t>
         </is>
       </c>
     </row>
